--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484158_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484158_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0682</v>
+        <v>4.6891</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9738</v>
+        <v>3.3422</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0944</v>
+        <v>1.3469</v>
       </c>
       <c r="G2" t="n">
         <v>3.4265</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6875</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5498</v>
+        <v>-0.1813</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1378</v>
+        <v>0.1147</v>
       </c>
       <c r="V2" t="n">
         <v>0.3373</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7565</v>
+        <v>2.1325</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1824</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4259</v>
+        <v>1.5564</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3125</v>
+        <v>0.2989</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0594</v>
+        <v>-0.459</v>
       </c>
       <c r="I3" t="n">
-        <v>1.372</v>
+        <v>0.758</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5293</v>
+        <v>0.6501</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3194</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>0.7255</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2168</v>
+        <v>-0.3512</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3788</v>
+        <v>-0.3837</v>
       </c>
       <c r="O3" t="n">
-        <v>0.162</v>
+        <v>0.0325</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6156</v>
+        <v>-0.1502</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2323</v>
+        <v>-0.34</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3833</v>
+        <v>0.1898</v>
       </c>
       <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.266</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.0757</v>
-      </c>
       <c r="X3" t="n">
-        <v>-1.8097</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6917</v>
+        <v>1.7909</v>
       </c>
       <c r="E4" t="n">
-        <v>0.703</v>
+        <v>0.5216</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9888</v>
+        <v>1.2693</v>
       </c>
       <c r="G4" t="n">
         <v>0.8018</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.102</v>
+        <v>-0.0028</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1304</v>
+        <v>-0.051</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2324</v>
+        <v>0.0481</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5538</v>
+        <v>1.3404</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0587</v>
+        <v>2.103</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6125</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2989</v>
+        <v>1.3125</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.459</v>
+        <v>-0.0594</v>
       </c>
       <c r="I5" t="n">
-        <v>0.758</v>
+        <v>1.372</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6501</v>
+        <v>1.5293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.3194</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7255</v>
+        <v>1.21</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3512</v>
+        <v>-0.2168</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3837</v>
+        <v>-0.3788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0325</v>
+        <v>0.162</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R5" t="n">
         <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.729</v>
+        <v>-1.0316</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9748</v>
+        <v>-0.3117</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2459</v>
+        <v>-0.72</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>2.0757</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NINOT PEDROSA</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8159</v>
+        <v>1.2718</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3615</v>
+        <v>-0.134</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5456</v>
+        <v>1.4058</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1907</v>
+        <v>1.2094</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6611</v>
+        <v>4.1633</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4704</v>
+        <v>-2.9539</v>
       </c>
       <c r="J6" t="n">
-        <v>1.563</v>
+        <v>1.4983</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2432</v>
+        <v>3.5389</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6802</v>
+        <v>-2.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3723</v>
+        <v>-0.2889</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4179</v>
+        <v>0.6244</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7902</v>
+        <v>-0.9133</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3667</v>
+        <v>-0.9296</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4348</v>
+        <v>-0.4876</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>M. NINOT PEDROSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8013</v>
+        <v>0.5379</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6045</v>
+        <v>1.0554</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4058</v>
+        <v>-0.5175</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2094</v>
+        <v>1.1907</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1633</v>
+        <v>2.6611</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9539</v>
+        <v>-1.4704</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4983</v>
+        <v>1.563</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5389</v>
+        <v>2.2432</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0406</v>
+        <v>-0.6802</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2889</v>
+        <v>-0.3723</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6244</v>
+        <v>0.4179</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9133</v>
+        <v>-0.7902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9125</v>
+        <v>-0.238</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4876</v>
+        <v>-0.4068</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0921</v>
+        <v>0.0002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.307</v>
+        <v>0.1029</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2149</v>
+        <v>-0.1027</v>
       </c>
       <c r="G8" t="n">
         <v>0.1467</v>
@@ -1078,13 +1078,13 @@
         <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4353</v>
+        <v>-0.5271</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1304</v>
+        <v>-0.0736</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5657</v>
+        <v>-0.4535</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0955</v>
+        <v>-0.2562</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0039</v>
+        <v>0.4549</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9084</v>
+        <v>-0.7111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9705</v>
+        <v>0.2918</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2449</v>
+        <v>0.6804</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2154</v>
+        <v>-0.3886</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2307</v>
+        <v>0.6706</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0845</v>
+        <v>0.6706</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3151</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7398</v>
+        <v>-0.3788</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1605</v>
+        <v>0.0098</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9003</v>
+        <v>-0.3886</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9677</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5135</v>
+        <v>-0.6788</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.544</v>
+        <v>-0.2834</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0575</v>
+        <v>-0.3954</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1469</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4085</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6005</v>
+        <v>-0.4758</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2508</v>
+        <v>-2.8792</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8512999999999999</v>
+        <v>2.4034</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2918</v>
+        <v>-0.9705</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6804</v>
+        <v>1.2449</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3886</v>
+        <v>-2.2154</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6706</v>
+        <v>-0.2307</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6706</v>
+        <v>1.0845</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.3151</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3788</v>
+        <v>-0.7398</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0098</v>
+        <v>0.1605</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3886</v>
+        <v>-0.9003</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3968</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1984</v>
+        <v>-3.9677</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0231</v>
+        <v>0.1332</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4874</v>
+        <v>-0.4193</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5357</v>
+        <v>0.5525</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>2.1469</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>1.7384</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.532</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0893</v>
+        <v>-0.9132</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8334</v>
+        <v>-1.6293</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7441</v>
+        <v>0.7161</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6657</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2171</v>
+        <v>-0.0411</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6744</v>
+        <v>-0.4704</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4574</v>
+        <v>0.4293</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3994</v>
+        <v>-4.8993</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3889</v>
+        <v>-4.001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0105</v>
+        <v>-0.8983</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5928</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0465</v>
+        <v>-0.4534</v>
       </c>
       <c r="T12" t="n">
-        <v>0.873</v>
+        <v>0.2608</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8265</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.594799999999999</v>
+        <v>5.218299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1109</v>
+        <v>-0.4874000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.705799999999998</v>
+        <v>5.7057</v>
       </c>
       <c r="G13" t="n">
         <v>5.449299999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>9.400599999999999</v>
+        <v>9.400599999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9511</v>
+        <v>-3.951099999999999</v>
       </c>
       <c r="J13" t="n">
         <v>7.7065</v>
@@ -1447,7 +1447,7 @@
         <v>8.549599999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8425000000000005</v>
+        <v>-0.8424999999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-2.257200000000001</v>
@@ -1468,13 +1468,13 @@
         <v>14.8786</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.0163</v>
+        <v>-4.3927</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1733</v>
+        <v>-2.5499</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.843</v>
+        <v>-1.8431</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7978999999999998</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9505</v>
+        <v>6.9844</v>
       </c>
       <c r="E14" t="n">
-        <v>7.1349</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1844</v>
+        <v>0.4844</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5649</v>
+        <v>0.5654</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7397</v>
+        <v>-2.5607</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1748</v>
+        <v>3.1261</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2586</v>
+        <v>2.7934</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0578</v>
+        <v>-0.3067</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2008</v>
+        <v>3.1001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6937</v>
+        <v>-2.228</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3181</v>
+        <v>-2.254</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3756</v>
+        <v>0.026</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1278</v>
+        <v>1.4624</v>
       </c>
       <c r="T14" t="n">
-        <v>3.146</v>
+        <v>0.4083</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0182</v>
+        <v>1.0541</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3373</v>
+        <v>4.5599</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0713</v>
+        <v>4.4886</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7531</v>
+        <v>5.3504</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0919</v>
+        <v>5.0943</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6612</v>
+        <v>0.256</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5654</v>
+        <v>3.5649</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.5607</v>
+        <v>3.7397</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1261</v>
+        <v>-0.1748</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7934</v>
+        <v>4.2586</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3067</v>
+        <v>4.0578</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1001</v>
+        <v>0.2008</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.228</v>
+        <v>-0.6937</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.254</v>
+        <v>-0.3181</v>
       </c>
       <c r="O15" t="n">
-        <v>0.026</v>
+        <v>-0.3756</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2311</v>
+        <v>1.5276</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001</v>
+        <v>1.1054</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2309</v>
+        <v>0.4222</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5599</v>
+        <v>-0.3373</v>
       </c>
       <c r="W15" t="n">
-        <v>4.4886</v>
+        <v>-0.0713</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7578</v>
+        <v>4.477</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7055</v>
+        <v>1.6238</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0523</v>
+        <v>2.8532</v>
       </c>
       <c r="G16" t="n">
         <v>0.8733</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1155</v>
+        <v>0.6037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8615</v>
+        <v>0.0568</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.254</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>1.8097</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5421</v>
+        <v>-0.0172</v>
       </c>
       <c r="E17" t="n">
-        <v>0.018</v>
+        <v>-1.2681</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5601</v>
+        <v>1.2509</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0147</v>
+        <v>-1.8437</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2016</v>
+        <v>-2.2829</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2164</v>
+        <v>0.4392</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0803</v>
+        <v>-1.5516</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-2.2369</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0803</v>
+        <v>0.6853</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.2921</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2016</v>
+        <v>-0.046</v>
       </c>
       <c r="O17" t="n">
-        <v>0.136</v>
+        <v>-0.2461</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0249</v>
+        <v>1.033</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0623</v>
+        <v>0.2835</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0374</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9771</v>
+        <v>-0.486</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2884</v>
+        <v>0.018</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3113</v>
+        <v>-0.504</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8437</v>
+        <v>0.0147</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2829</v>
+        <v>-0.2016</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4392</v>
+        <v>0.2164</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5516</v>
+        <v>0.0803</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2369</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6853</v>
+        <v>0.0803</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2921</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.046</v>
+        <v>-0.2016</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2461</v>
+        <v>0.136</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0731</v>
+        <v>0.0312</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7368</v>
+        <v>-0.0623</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8099</v>
+        <v>0.0935</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4573</v>
+        <v>-1.0671</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1135</v>
+        <v>-0.8074</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3439</v>
+        <v>-0.2597</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5329</v>
@@ -1936,13 +1936,13 @@
         <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1309</v>
+        <v>0.2593</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.187</v>
+        <v>0.1191</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8632</v>
+        <v>-1.4975</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3167</v>
+        <v>-0.8065</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5465</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5651</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1077</v>
+        <v>0.2579</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5157</v>
+        <v>0.3712</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4751</v>
+        <v>-1.9905</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5303</v>
+        <v>-2.7344</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0553</v>
+        <v>0.744</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0897</v>
@@ -2092,13 +2092,13 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5669</v>
+        <v>1.0515</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6803</v>
+        <v>0.4763</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1135</v>
+        <v>0.5752</v>
       </c>
       <c r="V21" t="n">
         <v>-2.5555</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2574</v>
+        <v>-4.047</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9983</v>
+        <v>-3.6961</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7409</v>
+        <v>-0.3509</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2682</v>
+        <v>-1.8369</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.8048</v>
+        <v>-1.3911</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5366</v>
+        <v>-0.4457</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8466</v>
+        <v>-1.3778</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.69</v>
+        <v>-0.66</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8434</v>
+        <v>-0.7178</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4216</v>
+        <v>-0.459</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1148</v>
+        <v>-0.7311</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6932</v>
+        <v>0.2721</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.579</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1661</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4708</v>
+        <v>-0.5555</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4229</v>
+        <v>-0.3344</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0479</v>
+        <v>-0.2211</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.881</v>
+        <v>-0.266</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3973</v>
+        <v>-4.8545</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7981</v>
+        <v>-3.4066</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5992</v>
+        <v>-1.4479</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8369</v>
+        <v>-3.3312</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3911</v>
+        <v>-2.3634</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4457</v>
+        <v>-0.9678</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3778</v>
+        <v>-1.128</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.66</v>
+        <v>-1.093</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7178</v>
+        <v>-0.0351</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.459</v>
+        <v>-2.2032</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7311</v>
+        <v>-1.2704</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2721</v>
+        <v>-0.9328</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3887</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9058</v>
+        <v>0.0638</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4364</v>
+        <v>-0.2947</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4693</v>
+        <v>0.3585</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0866</v>
+        <v>-5.4061</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6106</v>
+        <v>-6.2227</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.476</v>
+        <v>0.8166</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3312</v>
+        <v>-2.2682</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3634</v>
+        <v>-3.8048</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9678</v>
+        <v>1.5366</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.128</v>
+        <v>-1.8466</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.093</v>
+        <v>-2.69</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0351</v>
+        <v>0.8434</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2032</v>
+        <v>-0.4216</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2704</v>
+        <v>-1.1148</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9328</v>
+        <v>0.6932</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5871</v>
+        <v>-2.579</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9838</v>
+        <v>-4.1661</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1683</v>
+        <v>1.3221</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4988</v>
+        <v>0.1985</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3304</v>
+        <v>1.1236</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.881</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5947</v>
+        <v>-2.554100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7056</v>
+        <v>-5.705699999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1109</v>
+        <v>3.1516</v>
       </c>
       <c r="G25" t="n">
         <v>-5.4494</v>
@@ -2380,16 +2380,16 @@
         <v>2.2574</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8511000000000001</v>
+        <v>-0.8511000000000002</v>
       </c>
       <c r="L25" t="n">
         <v>3.1083</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.706599999999999</v>
+        <v>-7.7066</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.549299999999999</v>
+        <v>-8.549300000000001</v>
       </c>
       <c r="O25" t="n">
         <v>0.8425999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>9.9193</v>
       </c>
       <c r="S25" t="n">
-        <v>5.0166</v>
+        <v>7.056999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.843</v>
+        <v>1.8432</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1733</v>
+        <v>5.213900000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.7978000000000003</v>
@@ -2419,7 +2419,7 @@
         <v>5.0727</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.2748</v>
+        <v>-4.274800000000001</v>
       </c>
     </row>
   </sheetData>
